--- a/aircraft/reports/top-routes-bidirectional.xlsx
+++ b/aircraft/reports/top-routes-bidirectional.xlsx
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14">
@@ -602,7 +602,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EWR-FRA</t>
+          <t>BRU-JFK</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FRA-IAD</t>
+          <t>EWR-FRA</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -628,7 +628,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BRU-JFK</t>
+          <t>FRA-IAD</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CDG-DUB</t>
+          <t>BRU-DUB</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -654,7 +654,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BRU-DUB</t>
+          <t>BCN-MAN</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -667,7 +667,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BCN-MAN</t>
+          <t>CDG-DUB</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LBA-PMI</t>
+          <t>LUX-ORD</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -810,7 +810,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LUX-ORD</t>
+          <t>LBA-PMI</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AMS-ATL</t>
+          <t>BRU-YUL</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BRU-YUL</t>
+          <t>AMS-ATL</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -992,7 +992,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EDI-LGW</t>
+          <t>BHX-PMI</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1005,11 +1005,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MUC-YYZ</t>
+          <t>EDI-LGW</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BHX-PMI</t>
+          <t>MUC-YYZ</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EDI-PMI</t>
+          <t>AMS-LIM</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AMS-LIM</t>
+          <t>EDI-PMI</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ALC-BHX</t>
+          <t>CDG-SFO</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CDG-SFO</t>
+          <t>ALC-BHX</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DUB-LHR</t>
+          <t>CUN-FRA</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CUN-FRA</t>
+          <t>DUB-LHR</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ALC-EDI</t>
+          <t>CDG-JFK</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DUB-ZRH</t>
+          <t>DFW-FRA</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CDG-JFK</t>
+          <t>ALC-EDI</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DFW-FRA</t>
+          <t>DUB-ZRH</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AMS-GRU</t>
+          <t>LGG-MEM</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LGG-MEM</t>
+          <t>AMS-GRU</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GLA-PMI</t>
+          <t>ATH-LCA</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ATH-LCA</t>
+          <t>GLA-PMI</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CGN-MEM</t>
+          <t>MUC-YUL</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MUC-YUL</t>
+          <t>CGN-MEM</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AMS-BOS</t>
+          <t>BRU-MIA</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BRU-MIA</t>
+          <t>AMS-BOS</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FRA-LHR</t>
+          <t>AMS-BOG</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AMS-BOG</t>
+          <t>FRA-LHR</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AMS-CTG</t>
+          <t>DEN-FRA</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DEN-FRA</t>
+          <t>AMS-CTG</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BCN-EDI</t>
+          <t>DUB-FCO</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DUB-FCO</t>
+          <t>BCN-EDI</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CDG-HND</t>
+          <t>IST-JFK</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IST-JFK</t>
+          <t>CDG-HND</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AGP-MAN</t>
+          <t>YYZ-ZRH</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AMS-GYE</t>
+          <t>AGP-MAN</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EDI-GVA</t>
+          <t>AMS-GYE</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>YYZ-ZRH</t>
+          <t>EDI-GVA</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EWR-TLV</t>
+          <t>CDG-ORD</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CDG-ORD</t>
+          <t>EWR-TLV</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MAN-MLA</t>
+          <t>JFK-LUX</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JFK-LUX</t>
+          <t>FRA-MIA</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FRA-MIA</t>
+          <t>MAN-MLA</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FRA-MEX</t>
+          <t>LGW-RMU</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>AMS-AUA</t>
+          <t>BOS-MUC</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ORD-ZRH</t>
+          <t>CDG-YYZ</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CDG-YYZ</t>
+          <t>AMS-AUA</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>JFK-MUC</t>
+          <t>FRA-MEX</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BOS-MUC</t>
+          <t>LPL-PMI</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LPL-PMI</t>
+          <t>ORD-ZRH</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LGW-RMU</t>
+          <t>JFK-MUC</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>IST-LHR</t>
+          <t>LCA-LHR</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LCA-LHR</t>
+          <t>IST-LHR</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EDI-LHR</t>
+          <t>CDG-LHR</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CDG-LHR</t>
+          <t>EDI-LHR</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DUB-MUC</t>
+          <t>BVA-DUB</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>BVA-DUB</t>
+          <t>DUB-MUC</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ATL-LUX</t>
+          <t>GVA-LHR</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>GVA-LHR</t>
+          <t>DTW-FRA</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DTW-FRA</t>
+          <t>MAN-ZRH</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MAN-ZRH</t>
+          <t>ATL-LUX</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ALC-LPL</t>
+          <t>BHX-FAO</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CDG-NCL</t>
+          <t>MAN-REU</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>AMS-SXM</t>
+          <t>LHR-NCE</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ALC-LGW</t>
+          <t>AMS-GIG</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>AMS-GIG</t>
+          <t>ALC-LPL</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>BHX-FAO</t>
+          <t>ALC-LGW</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MAN-REU</t>
+          <t>CDG-NCL</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>LHR-NCE</t>
+          <t>AMS-SXM</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MAN-VLC</t>
+          <t>IAD-LHR</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DUB-VCE</t>
+          <t>IAD-VIE</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>LGG-ORD</t>
+          <t>EDI-IBZ</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EDI-IBZ</t>
+          <t>DUB-VCE</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>IAD-LHR</t>
+          <t>LGG-ORD</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>IAD-VIE</t>
+          <t>FRA-TPA</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FRA-TPA</t>
+          <t>MAN-VLC</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>DUB-DXB</t>
+          <t>IAD-ZRH</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>BHX-JER</t>
+          <t>BHD-LGW</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>AGP-BHX</t>
+          <t>AMS-PHL</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>AMS-PHL</t>
+          <t>DUB-DXB</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ATL-LGG</t>
+          <t>BHX-JER</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>IAD-ZRH</t>
+          <t>ATH-LHR</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>LHR-SIN</t>
+          <t>AGP-BHX</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ATH-LHR</t>
+          <t>ATL-LGG</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>BHD-LGW</t>
+          <t>LHR-SIN</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>FCO-MAN</t>
+          <t>IAH-LUX</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>IAH-LUX</t>
+          <t>LHR-SFO</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ATL-MUC</t>
+          <t>FCO-MAN</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>LHR-SFO</t>
+          <t>ATL-MUC</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>FRA-SFO</t>
+          <t>CDG-PIK</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>FRA-PHL</t>
+          <t>EMA-TFS</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>EMA-TFS</t>
+          <t>FRA-SFO</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>CDG-PIK</t>
+          <t>FRA-PHL</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>CDG-MEM</t>
+          <t>BCN-LPL</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>BCN-LPL</t>
+          <t>CDG-MEM</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>DBV-DUB</t>
+          <t>JFK-MXP</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MAH-MAN</t>
+          <t>DBV-DUB</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>JFK-MXP</t>
+          <t>MAH-MAN</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>DOH-ORD</t>
+          <t>JFK-ZRH</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>AMS-LGW</t>
+          <t>EMA-PMI</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>EMA-PMI</t>
+          <t>DOH-ORD</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>JFK-ZRH</t>
+          <t>AMS-LGW</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>HHN-KIR</t>
+          <t>DXB-JFK</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>AUH-IAD</t>
+          <t>HHN-KIR</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>HND-LHR</t>
+          <t>BCN-LHR</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>CPH-LHR</t>
+          <t>EWR-VIE</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>BCN-LHR</t>
+          <t>AUH-IAD</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>EWR-VIE</t>
+          <t>DUS-LHR</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>DUS-LHR</t>
+          <t>EMA-FAO</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>EMA-FAO</t>
+          <t>CPH-LHR</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>AMS-UIO</t>
+          <t>DOH-JFK</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>DOH-JFK</t>
+          <t>JFK-TLV</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>JER-MAN</t>
+          <t>HND-LHR</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>JFK-TLV</t>
+          <t>JER-MAN</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>DXB-JFK</t>
+          <t>AMS-UIO</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>AMS-CUN</t>
+          <t>BHX-GVA</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>BHX-GVA</t>
+          <t>AMS-YYZ</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>IND-LUX</t>
+          <t>AMS-IAH</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>FRA-YHZ</t>
+          <t>IBZ-LBA</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>AMS-YYZ</t>
+          <t>DUB-FMM</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>IBZ-LBA</t>
+          <t>IND-LUX</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>AMS-IAH</t>
+          <t>BHX-IBZ</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>DUB-FMM</t>
+          <t>CGN-DUB</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>DEN-MUC</t>
+          <t>ISL-SNN</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>CGN-DUB</t>
+          <t>BRU-LHR</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ISL-SNN</t>
+          <t>IBZ-NCL</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>BRU-LHR</t>
+          <t>AMS-CUN</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>BHX-IBZ</t>
+          <t>DOH-IAD</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>GLA-LHR</t>
+          <t>DEN-MUC</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>DOH-IAD</t>
+          <t>FRA-YHZ</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3332,11 +3332,11 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>CIA-MAN</t>
+          <t>GLA-LHR</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="225">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>DFW-LUX</t>
+          <t>CDG-DFW</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>CDG-DFW</t>
+          <t>CIA-MAN</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>LHR-MIA</t>
+          <t>DFW-LUX</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>JFK-KWI</t>
+          <t>LHR-MIA</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>JER-LGW</t>
+          <t>JFK-KWI</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>MAN-PSA</t>
+          <t>ALC-PIK</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>AUH-JFK</t>
+          <t>ATH-EWR</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>IBZ-NCL</t>
+          <t>BRU-PUJ</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>FCO-LHR</t>
+          <t>MAN-NBE</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>CLT-FRA</t>
+          <t>JER-LGW</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>MAN-NBE</t>
+          <t>CLT-FRA</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>ATH-EWR</t>
+          <t>FCO-LHR</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>BRU-PUJ</t>
+          <t>AUH-JFK</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>ALC-PIK</t>
+          <t>MAN-PSA</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>DFW-LHR</t>
+          <t>LHR-VIE</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>AMS-SJO</t>
+          <t>HAM-LHR</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>LHR-VIE</t>
+          <t>GCI-MAN</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>GCI-MAN</t>
+          <t>BHX-TFS</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>HAM-LHR</t>
+          <t>AMS-SJO</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>BGY-MAN</t>
+          <t>ABZ-LHR</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>BHX-TFS</t>
+          <t>LHR-YVR</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>LHR-YVR</t>
+          <t>DFW-LHR</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>ACE-BHX</t>
+          <t>BGY-MAN</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>BRS-CPH</t>
+          <t>DOH-PHL</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>GRO-MAN</t>
+          <t>ACE-BHX</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>IST-MIA</t>
+          <t>BOS-CDG</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>DOH-PHL</t>
+          <t>BRS-CPH</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>BOS-CDG</t>
+          <t>GRO-MAN</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -3722,11 +3722,11 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>CIA-DUB</t>
+          <t>IST-MIA</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="255">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>ABZ-LHR</t>
+          <t>LCA-VIE</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>DOH-YUL</t>
+          <t>AMS-POS</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>HEL-LHR</t>
+          <t>BRU-DFW</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>MIA-WAW</t>
+          <t>BHX-GCI</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>DUB-NCE</t>
+          <t>CPH-LGW</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>BHX-GCI</t>
+          <t>DUB-NCE</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>BRU-DFW</t>
+          <t>MIA-WAW</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>AMS-POS</t>
+          <t>DOH-YUL</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>LGW-MAD</t>
+          <t>CIA-DUB</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>LCA-VIE</t>
+          <t>HEL-LHR</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>CPH-LGW</t>
+          <t>LGW-MAD</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>IAD-IST</t>
+          <t>SNN-WRO</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>SNN-WRO</t>
+          <t>DUB-LIN</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>DUB-LIN</t>
+          <t>CDG-GLA</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>EMA-JER</t>
+          <t>AMS-CWL</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>FCO-JFK</t>
+          <t>SNN-STN</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>SFO-ZRH</t>
+          <t>DUB-LYS</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>AMS-CWL</t>
+          <t>GLA-SOU</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>GLA-SOU</t>
+          <t>SFO-ZRH</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>DUB-LYS</t>
+          <t>FCO-JFK</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>CDG-GLA</t>
+          <t>EMA-JER</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>SNN-STN</t>
+          <t>IAD-IST</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>AGP-LGW</t>
+          <t>BGR-LUX</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>BOM-LHR</t>
+          <t>BHD-SOU</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>AMM-JFK</t>
+          <t>AKT-BZZ</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>CGN-IND</t>
+          <t>BOM-LHR</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>LGW-VCE</t>
+          <t>GVA-LGW</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>GVA-LGW</t>
+          <t>AGP-LGW</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>ARN-LHR</t>
+          <t>DUB-MXP</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>DUB-MXP</t>
+          <t>AMM-JFK</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>GLA-REU</t>
+          <t>DUB-LTN</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>BGR-LUX</t>
+          <t>LGW-VCE</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>BHD-SOU</t>
+          <t>ARN-LHR</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>DUB-LTN</t>
+          <t>GLA-REU</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>AKT-BZZ</t>
+          <t>CGN-IND</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>BOS-DOH</t>
+          <t>GVA-LPL</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>ORK-POZ</t>
+          <t>JER-LPL</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>DUB-MRS</t>
+          <t>ORK-POZ</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>GVA-LPL</t>
+          <t>BOS-DOH</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>LHR-PVG</t>
+          <t>DUB-MRS</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>ICN-LHR</t>
+          <t>BOS-IST</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>JER-LPL</t>
+          <t>LHR-PVG</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>LHR-OSL</t>
+          <t>ICN-LHR</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>CDG-MEX</t>
+          <t>LPL-NCE</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>LPL-NCE</t>
+          <t>CDG-MEX</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>LHR-VCE</t>
+          <t>DXB-YYZ</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>BER-LHR</t>
+          <t>LHR-VCE</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>CPH-LCA</t>
+          <t>BCN-GLA</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>IOM-LGW</t>
+          <t>BER-LHR</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>LGG-YHZ</t>
+          <t>CPH-LCA</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>KEF-LGW</t>
+          <t>IOM-LGW</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>DXB-YYZ</t>
+          <t>LCA-LGW</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>LCA-LGW</t>
+          <t>LGG-YHZ</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>BOS-IST</t>
+          <t>KEF-LGW</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>BCN-GLA</t>
+          <t>LHR-OSL</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>BEG-LCA</t>
+          <t>LCA-SKG</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>LCA-SKG</t>
+          <t>BEG-LCA</t>
         </is>
       </c>
       <c r="C316" t="n">

--- a/aircraft/reports/top-routes-bidirectional.xlsx
+++ b/aircraft/reports/top-routes-bidirectional.xlsx
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11">
@@ -641,11 +641,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BRU-DUB</t>
+          <t>BCN-MAN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18">
@@ -654,7 +654,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BCN-MAN</t>
+          <t>BRU-DUB</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AMS-BOS</t>
+          <t>FRA-LHR</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FRA-LHR</t>
+          <t>AMS-BOS</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BOS-LHR</t>
+          <t>IST-JFK</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1512,11 +1512,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DUB-FCO</t>
+          <t>BOS-LHR</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="85">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IST-JFK</t>
+          <t>DUB-FCO</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>YYZ-ZRH</t>
+          <t>AMS-GYE</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AGP-MAN</t>
+          <t>YYZ-ZRH</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AMS-GYE</t>
+          <t>EDI-GVA</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EDI-GVA</t>
+          <t>AGP-MAN</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CDG-ORD</t>
+          <t>EWR-TLV</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EWR-TLV</t>
+          <t>CDG-ORD</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GSP-HHN</t>
+          <t>AMS-MEX</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AMS-MEX</t>
+          <t>EMA-GCI</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EMA-GCI</t>
+          <t>GSP-HHN</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LHR-MAD</t>
+          <t>FRA-MIA</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LHR-MAN</t>
+          <t>LHR-MAD</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>AMS-AUA</t>
+          <t>LHR-MAN</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MAN-MLA</t>
+          <t>AMS-AUA</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FRA-MIA</t>
+          <t>LPL-PMI</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -1785,11 +1785,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ORD-ZRH</t>
+          <t>MAN-MLA</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="106">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LPL-PMI</t>
+          <t>BOS-MUC</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FRA-MEX</t>
+          <t>CDG-YYZ</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LGW-RMU</t>
+          <t>BGY-DUB</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CDG-YYZ</t>
+          <t>ORD-ZRH</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BOS-MUC</t>
+          <t>JFK-MUC</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>JFK-MUC</t>
+          <t>FRA-MEX</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -1876,11 +1876,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BGY-DUB</t>
+          <t>LGW-RMU</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="113">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LHR-ORD</t>
+          <t>EDI-LHR</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EDI-LHR</t>
+          <t>LHR-ORD</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>GVA-LHR</t>
+          <t>MAN-ZRH</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MAN-ZRH</t>
+          <t>ATL-LUX</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ATL-LUX</t>
+          <t>GVA-LHR</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>BHX-FAO</t>
+          <t>AMS-GIG</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MAN-REU</t>
+          <t>AMS-SXM</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>LHR-NCE</t>
+          <t>BHX-FAO</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>AMS-GIG</t>
+          <t>CDG-NCL</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ALC-LPL</t>
+          <t>ALC-LGW</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ALC-LGW</t>
+          <t>MAN-REU</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CDG-NCL</t>
+          <t>LHR-NCE</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>AMS-SXM</t>
+          <t>ALC-LPL</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>IAD-VIE</t>
+          <t>DUB-VCE</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EDI-IBZ</t>
+          <t>LGG-ORD</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>DUB-VCE</t>
+          <t>MAN-VLC</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>LGG-ORD</t>
+          <t>IAD-VIE</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FRA-TPA</t>
+          <t>BHD-LGW</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MAN-VLC</t>
+          <t>FRA-TPA</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2526,11 +2526,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>IAD-ZRH</t>
+          <t>EDI-IBZ</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="163">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>BHD-LGW</t>
+          <t>IAD-ZRH</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DUB-DXB</t>
+          <t>CDG-SEA</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CDG-SEA</t>
+          <t>LHR-SIN</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>AGP-BHX</t>
+          <t>BHX-JER</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ATL-LGG</t>
+          <t>DUB-DXB</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>LHR-SIN</t>
+          <t>ATL-LGG</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>BHX-JER</t>
+          <t>AGP-BHX</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>DOH-LHR</t>
+          <t>BCN-LPL</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>IAH-LUX</t>
+          <t>ATL-MUC</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>LHR-SFO</t>
+          <t>DOH-LHR</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>FCO-MAN</t>
+          <t>IAH-LUX</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ATL-MUC</t>
+          <t>LHR-SFO</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CDG-PIK</t>
+          <t>MAH-MAN</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>EMA-TFS</t>
+          <t>FRA-SFO</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>FRA-SFO</t>
+          <t>FCO-MAN</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>FRA-PHL</t>
+          <t>EMA-TFS</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>BCN-LPL</t>
+          <t>CDG-PIK</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -2799,11 +2799,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>IST-YYZ</t>
+          <t>FRA-PHL</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="184">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>JFK-MXP</t>
+          <t>DBV-DUB</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>DBV-DUB</t>
+          <t>DOH-ORD</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>BFS-CDG</t>
+          <t>AGP-EMA</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>AGP-EMA</t>
+          <t>JFK-ZRH</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PIK-PMI</t>
+          <t>IST-YYZ</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MAH-MAN</t>
+          <t>EMA-PMI</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>JFK-ZRH</t>
+          <t>JFK-MXP</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>EMA-PMI</t>
+          <t>BFS-CDG</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>DOH-ORD</t>
+          <t>MAN-NCE</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>MAN-NCE</t>
+          <t>PIK-PMI</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>DXB-JFK</t>
+          <t>BCN-LHR</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>BCN-LHR</t>
+          <t>ATL-LHR</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>EWR-VIE</t>
+          <t>CPH-LHR</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ATL-LHR</t>
+          <t>EWR-VIE</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>DUS-LHR</t>
+          <t>HND-LHR</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>EMA-FAO</t>
+          <t>DUS-LHR</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>CPH-LHR</t>
+          <t>DXB-JFK</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>DOH-JFK</t>
+          <t>AMS-UIO</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JFK-TLV</t>
+          <t>JER-MAN</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>HND-LHR</t>
+          <t>DOH-JFK</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>JER-MAN</t>
+          <t>IBZ-NCL</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>AMS-UIO</t>
+          <t>EMA-FAO</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3137,11 +3137,11 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>BHX-GVA</t>
+          <t>JFK-TLV</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="210">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>AMS-YYZ</t>
+          <t>FRA-YHZ</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>AMS-IAH</t>
+          <t>IBZ-LBA</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>IBZ-LBA</t>
+          <t>GLA-LHR</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>DUB-FMM</t>
+          <t>ISL-SNN</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>IND-LUX</t>
+          <t>AMS-IAH</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>BHX-IBZ</t>
+          <t>CGN-DUB</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>CGN-DUB</t>
+          <t>BHX-GVA</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ISL-SNN</t>
+          <t>DUB-FMM</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>BRU-LHR</t>
+          <t>BHX-IBZ</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>IBZ-NCL</t>
+          <t>AMS-YYZ</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>DOH-IAD</t>
+          <t>DEN-MUC</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>DEN-MUC</t>
+          <t>DOH-IAD</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>FRA-YHZ</t>
+          <t>BRU-LHR</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>GLA-LHR</t>
+          <t>IND-LUX</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>CDG-DFW</t>
+          <t>CIA-MAN</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>CIA-MAN</t>
+          <t>CDG-DFW</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>CLT-FRA</t>
+          <t>AUH-JFK</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>JFK-KWI</t>
+          <t>FCO-LHR</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>MAN-PSA</t>
+          <t>CLT-FRA</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>AUH-JFK</t>
+          <t>ACE-BHX</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>FCO-LHR</t>
+          <t>MAN-PSA</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -3527,11 +3527,11 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>BGY-MAN</t>
+          <t>JFK-KWI</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="240">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>HAM-LHR</t>
+          <t>LHR-VIE</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>AMS-SJO</t>
+          <t>HAM-LHR</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>ABZ-LHR</t>
+          <t>AMS-SJO</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>LHR-VIE</t>
+          <t>ABZ-LHR</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>LHR-YVR</t>
+          <t>BGY-MAN</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>IST-MIA</t>
+          <t>DOH-PHL</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>DOH-PHL</t>
+          <t>IST-MIA</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>GRO-MAN</t>
+          <t>LHR-YVR</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>BOS-CDG</t>
+          <t>GRO-MAN</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>BRS-CPH</t>
+          <t>BOS-CDG</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>CDG-GLA</t>
+          <t>BRS-CPH</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>IST-ORD</t>
+          <t>CDG-GLA</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>ACE-BHX</t>
+          <t>IST-ORD</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>HEL-LHR</t>
+          <t>GLA-REU</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>DUB-NCE</t>
+          <t>AMM-JFK</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>AMM-JFK</t>
+          <t>DUB-NCE</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>DOH-YUL</t>
+          <t>LCA-VIE</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>CIA-DUB</t>
+          <t>DOH-YUL</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>MIA-WAW</t>
+          <t>CIA-DUB</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>LCA-VIE</t>
+          <t>MIA-WAW</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>LGW-MAD</t>
+          <t>HEL-LHR</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>CPH-LGW</t>
+          <t>LGW-MAD</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>EMA-JER</t>
+          <t>CPH-LGW</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>AMS-CWL</t>
+          <t>DOH-DUB</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>SNN-STN</t>
+          <t>AMS-CWL</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>DUB-LYS</t>
+          <t>SNN-STN</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>GLA-SOU</t>
+          <t>DUB-LYS</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>SNN-WRO</t>
+          <t>GLA-SOU</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>IAD-IST</t>
+          <t>EMA-JER</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>DOH-DUB</t>
+          <t>IAD-IST</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4060,11 +4060,11 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>CVG-LEJ</t>
+          <t>SNN-WRO</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="281">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>BGR-LUX</t>
+          <t>DUB-MXP</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>BOM-LHR</t>
+          <t>CVG-LEJ</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>GLA-REU</t>
+          <t>DUB-LTN</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>GVA-LGW</t>
+          <t>LPL-NCE</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>AGP-LGW</t>
+          <t>GVA-LGW</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>AKT-BZZ</t>
+          <t>AGP-LGW</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>DUB-MXP</t>
+          <t>AKT-BZZ</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>ARN-LHR</t>
+          <t>BOM-LHR</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>LGW-VCE</t>
+          <t>BGR-LUX</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>BHD-SOU</t>
+          <t>ARN-LHR</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>DUB-LTN</t>
+          <t>LGW-VCE</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4229,11 +4229,11 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>JER-LPL</t>
+          <t>BHD-SOU</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="294">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>GVA-LPL</t>
+          <t>BOS-DOH</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>BOS-DOH</t>
+          <t>GVA-LPL</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>ORK-POZ</t>
+          <t>DUB-MRS</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>DUB-MRS</t>
+          <t>ORK-POZ</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>ICN-LHR</t>
+          <t>BCN-GLA</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>BOS-IST</t>
+          <t>ICN-LHR</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>CPH-LCA</t>
+          <t>BOS-IST</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>BCN-GLA</t>
+          <t>CPH-LCA</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>CDG-MEX</t>
+          <t>JER-LPL</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>LPL-NCE</t>
+          <t>CDG-MEX</t>
         </is>
       </c>
       <c r="C304" t="n">
